--- a/omf-example-plugin/src/main/java/com/samares_engineering/omf/omf_example_plugin/features/excel_to_parametric/UAV MOE Equation.xlsx
+++ b/omf-example-plugin/src/main/java/com/samares_engineering/omf/omf_example_plugin/features/excel_to_parametric/UAV MOE Equation.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QuentinCespedes\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\java\mdplugins\OMF\OMF_Private\omf-example-plugin\src\main\java\com\samares_engineering\omf\omf_example_plugin\features\excel_to_parametric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883822DD-40E6-420D-89AB-C87096F5D97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2AE45D-B832-477E-BAAF-ABFB79919A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{A22A8A54-8611-4DA6-995F-F1DD76DD8434}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14670" windowHeight="10545" xr2:uid="{A22A8A54-8611-4DA6-995F-F1DD76DD8434}"/>
+    <workbookView xWindow="-105" yWindow="10440" windowWidth="14670" windowHeight="10545" activeTab="1" xr2:uid="{ECDD6195-D704-4DB1-91AF-46E52C29149A}"/>
   </bookViews>
   <sheets>
     <sheet name="ValueProperties" sheetId="1" r:id="rId1"/>
@@ -37,44 +38,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
-  <si>
-    <t>heures</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
   <si>
     <t>min</t>
   </si>
   <si>
-    <t>Temps total mission = Temps Traitement Total + Temps Refuel Total + 2 * Temps base-champs + temps de recharge batterie</t>
-  </si>
-  <si>
-    <t>Durée recharge totale = nombre de recharge * ( vitesse de recharge + Temps trajet Base-Champ)</t>
-  </si>
-  <si>
-    <t>Temps de rechages batterie TOTAL</t>
-  </si>
-  <si>
-    <t>Énergie nécessaire pour la mission / Capacité de la batterie</t>
-  </si>
-  <si>
-    <t>Nombre de recharges de batterie</t>
-  </si>
-  <si>
     <t>kw</t>
   </si>
   <si>
-    <t>(Temps traitement * Efficacité énergétique * (Poids structure + Poids produit + Poids batterie))</t>
-  </si>
-  <si>
-    <t>Nombre de recharges produit * (Temps de refuel + Temps trajet Base-Champ)</t>
-  </si>
-  <si>
-    <t>Nombre de recharges de produit</t>
-  </si>
-  <si>
-    <t>Nombre de rangées</t>
-  </si>
-  <si>
     <t>hectare</t>
   </si>
   <si>
@@ -87,36 +58,9 @@
     <t>Parameter</t>
   </si>
   <si>
-    <t>Longueur champ * Largeur champ</t>
-  </si>
-  <si>
-    <t>Surface champ * Dose appliquée</t>
-  </si>
-  <si>
-    <t>Largeur champ / Largeur d'application</t>
-  </si>
-  <si>
-    <t>Longueur champ / Vitesse moyenne</t>
-  </si>
-  <si>
-    <t>(Temps traitement rangée + Temps demi-tour) * Nombre de rangées</t>
-  </si>
-  <si>
-    <t>Produit nécessaire / Capacité du réservoir</t>
-  </si>
-  <si>
-    <t>Temps trajet recharge produit</t>
-  </si>
-  <si>
-    <t>Nombre de recharges de produit * Temps de trajet base-champ</t>
-  </si>
-  <si>
     <t>Formated</t>
   </si>
   <si>
-    <t>Distance Base-Field / Max Speed</t>
-  </si>
-  <si>
     <t>unit</t>
   </si>
   <si>
@@ -132,36 +76,9 @@
     <t>wat hours</t>
   </si>
   <si>
-    <t>Surface du champ</t>
-  </si>
-  <si>
-    <t>Produit nécessaire</t>
-  </si>
-  <si>
-    <t>Temps de traitement par rangée</t>
-  </si>
-  <si>
-    <t>Temps de traitement total</t>
-  </si>
-  <si>
-    <t>Temps de refuel total</t>
-  </si>
-  <si>
-    <t>Énergie nécessaire pour la mission</t>
-  </si>
-  <si>
-    <t>Temps de trajet base-champ</t>
-  </si>
-  <si>
-    <t>Durée totale de la mission</t>
-  </si>
-  <si>
     <t>hour</t>
   </si>
   <si>
-    <t>Durée totale de la mission/3600</t>
-  </si>
-  <si>
     <t>meter</t>
   </si>
   <si>
@@ -177,65 +94,158 @@
     <t>kilogram</t>
   </si>
   <si>
-    <t>watt jour per kilograme</t>
-  </si>
-  <si>
     <t>watt hour</t>
   </si>
   <si>
-    <t>Longueur du champ</t>
-  </si>
-  <si>
-    <t>Largeur du champ</t>
-  </si>
-  <si>
-    <t>Distance Base-Field</t>
-  </si>
-  <si>
-    <t>Latteral SOI Range</t>
-  </si>
-  <si>
-    <t>Vitesse moyenne</t>
-  </si>
-  <si>
     <t>Max Speed</t>
   </si>
   <si>
-    <t>Temps de demi-tour</t>
-  </si>
-  <si>
-    <t>Capacité du réservoir</t>
-  </si>
-  <si>
-    <t>Dose appliquée</t>
-  </si>
-  <si>
-    <t>Temps de refuel</t>
-  </si>
-  <si>
-    <t>Poids de la structure</t>
-  </si>
-  <si>
-    <t>Poids du produit transporté</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Efficacité énergétique </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poids de la batterie </t>
-  </si>
-  <si>
-    <t>Capacité de la batterie</t>
-  </si>
-  <si>
-    <t>Vitesse de recharge de batterie</t>
+    <t>Field Length</t>
+  </si>
+  <si>
+    <t>Field Width</t>
+  </si>
+  <si>
+    <t>Base-Field Distance</t>
+  </si>
+  <si>
+    <t>Lateral SOI Range</t>
+  </si>
+  <si>
+    <t>Average Speed</t>
+  </si>
+  <si>
+    <t>Tank Capacity</t>
+  </si>
+  <si>
+    <t>Applied Dose</t>
+  </si>
+  <si>
+    <t>Refuel Time</t>
+  </si>
+  <si>
+    <t>Structure Weight</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Battery Weight</t>
+  </si>
+  <si>
+    <t>Battery Capacity</t>
+  </si>
+  <si>
+    <t>Battery Recharge Speed</t>
+  </si>
+  <si>
+    <t>Field Area</t>
+  </si>
+  <si>
+    <t>Product Needed</t>
+  </si>
+  <si>
+    <t>Number of Rows</t>
+  </si>
+  <si>
+    <t>Number of Product Refills</t>
+  </si>
+  <si>
+    <t>Product Refill Travel Time</t>
+  </si>
+  <si>
+    <t>Total Refuel Time</t>
+  </si>
+  <si>
+    <t>Energy Needed for Mission</t>
+  </si>
+  <si>
+    <t>Number of Battery Recharges</t>
+  </si>
+  <si>
+    <t>Total Battery Recharge Time</t>
+  </si>
+  <si>
+    <t>Base-Field Travel Time</t>
+  </si>
+  <si>
+    <t>Total Mission Duration</t>
+  </si>
+  <si>
+    <t>Field Length * Field Width</t>
+  </si>
+  <si>
+    <t>Field Area * Applied Dose</t>
+  </si>
+  <si>
+    <t>Field Width / Application Width</t>
+  </si>
+  <si>
+    <t>Field Length / Average Speed</t>
+  </si>
+  <si>
+    <t>(Row Processing Time + Turnaround Time) * Number of Rows</t>
+  </si>
+  <si>
+    <t>Product Needed / Tank Capacity</t>
+  </si>
+  <si>
+    <t>Number of Product Refills * Base-Field Travel Time</t>
+  </si>
+  <si>
+    <t>Number of Product Refills * (Refuel Time + Base-Field Travel Time)</t>
+  </si>
+  <si>
+    <t>Energy Needed for Mission / Battery Capacity</t>
+  </si>
+  <si>
+    <t>Total Recharge Duration = Number of Recharges * (Recharge Speed + Base-Field Travel Time)</t>
+  </si>
+  <si>
+    <t>Base-Field Distance / Max Speed</t>
+  </si>
+  <si>
+    <t>Total Mission Duration / 3600</t>
+  </si>
+  <si>
+    <t>Turn around time</t>
+  </si>
+  <si>
+    <t>watt joul per kilograme</t>
+  </si>
+  <si>
+    <t>Row Treating Time</t>
+  </si>
+  <si>
+    <t>Total Treating Time</t>
+  </si>
+  <si>
+    <t>Total Mission Time = Total treatment Time + Total Refuel Time + 2 * Base-Field Travel Time + Battery Recharge Time</t>
+  </si>
+  <si>
+    <t>kilograme</t>
+  </si>
+  <si>
+    <t>(Processing Time * Energy Efficiency * Total system mass)</t>
+  </si>
+  <si>
+    <t>Total System mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Structure Weight + Transported Product Weight + Battery Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transported Product Weight </t>
+  </si>
+  <si>
+    <t>Tank capacity*1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,14 +270,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
@@ -283,14 +285,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,6 +353,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,9 +414,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -409,17 +437,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,203 +786,236 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F39931-1C93-41B6-BB89-874B75E18699}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="88.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="88.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="8">
+        <v>500</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="9">
+        <v>300</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="10">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6">
         <v>15</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="7">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="11">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="9">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="10">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="B10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="13">
+        <v>120</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="14">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="D12">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="13">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="14">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="16">
-        <v>15</v>
+      <c r="C13" s="15">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>46</v>
+        <v>30</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="C14" s="16">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="17">
-        <v>5</v>
+      <c r="A15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>47</v>
+        <v>32</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>12</v>
       </c>
       <c r="C16" s="5">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="6">
         <v>3</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -960,384 +1025,353 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA56FD2-2E8C-4F98-9B5F-251C6FDF40B3}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" customWidth="1"/>
-    <col min="3" max="3" width="110.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="21">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="19">
         <f>ValueProperties!C2*ValueProperties!C3</f>
         <v>150000</v>
       </c>
-      <c r="E2" s="2">
-        <f>D2</f>
-        <v>150000</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="E2" s="1">
         <f>D2/10000</f>
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="22">
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="19">
+        <f>ValueProperties!C3/ValueProperties!C5</f>
+        <v>30</v>
+      </c>
+      <c r="E3" s="1">
+        <f>D3</f>
+        <v>30</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="20">
         <f>D2*ValueProperties!C10</f>
         <v>3000</v>
       </c>
-      <c r="E3">
-        <f>D3</f>
+      <c r="E4">
+        <f>D4</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="22">
-        <f>ValueProperties!C3/ValueProperties!C5</f>
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E10" si="0">D4</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="22">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="20">
         <f>ValueProperties!C3/ValueProperties!C6</f>
         <v>300</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f>D5</f>
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="21">
-        <f>(D5+ValueProperties!C8)*D4</f>
+    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="19">
+        <f>(D5+ValueProperties!C8)*D3</f>
         <v>9300</v>
       </c>
-      <c r="E6" s="2">
-        <f t="shared" si="0"/>
-        <v>9300</v>
-      </c>
-      <c r="F6" s="2">
-        <f>D6/60</f>
-        <v>155</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <f>TRUNC(F6/60,1)</f>
+      <c r="E6" s="30">
+        <f>TRUNC(D6/3600,1)</f>
         <v>2.5</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="21">
+        <f>D4/ValueProperties!C9</f>
+        <v>200</v>
+      </c>
+      <c r="E7" s="27">
+        <f>D7</f>
+        <v>200</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="23">
-        <f>D3/ValueProperties!C9</f>
-        <v>200</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="22">
-        <f>D7*D13</f>
+      <c r="C8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="20">
+        <f>D7*D15</f>
         <v>13333.333333333334</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>13333.333333333334</v>
-      </c>
-      <c r="F8">
-        <f>D8/60</f>
-        <v>222.22222222222223</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <f>TRUNC(F8/60,1)</f>
+        <f>TRUNC(D8/3600,1)</f>
         <v>3.7</v>
       </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="21">
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="19">
         <f>D7*ValueProperties!C11 +D8</f>
         <v>37333.333333333336</v>
       </c>
-      <c r="E9" s="2">
-        <f t="shared" si="0"/>
-        <v>37333.333333333336</v>
-      </c>
-      <c r="F9" s="2">
-        <f>D9/60</f>
-        <v>622.22222222222229</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2">
-        <f>TRUNC(F9/60,1)</f>
+      <c r="E9" s="28">
+        <f>TRUNC(D9/3600,1)</f>
         <v>10.3</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="20">
+        <f>ValueProperties!C9</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="20">
+        <f>(ValueProperties!C14+D10+ValueProperties!C12)</f>
         <v>30</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="23">
-        <f>D6/3600*ValueProperties!C14*(ValueProperties!C15+ValueProperties!C13+ValueProperties!C12)</f>
-        <v>7750.0000000000009</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>7750.0000000000009</v>
-      </c>
-      <c r="F10" s="3">
-        <f>D10/1000</f>
-        <v>7.7500000000000009</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="22">
-        <f>D10/ValueProperties!C16</f>
-        <v>2.5833333333333335</v>
       </c>
       <c r="E11">
         <f>ROUNDUP(D11,1)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="21">
+        <f>D6/3600*ValueProperties!C13*D11</f>
+        <v>7750.0000000000009</v>
+      </c>
+      <c r="E12" s="2">
+        <f>D12/1000</f>
+        <v>7.7500000000000009</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="20">
+        <f>D12/ValueProperties!C15</f>
+        <v>2.5833333333333335</v>
+      </c>
+      <c r="E13">
+        <f>ROUNDUP(D13,1)</f>
         <v>2.6</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="21">
-        <f>D11*(ValueProperties!C17*3600+D13)</f>
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="19">
+        <f>D13*(ValueProperties!C16*3600+D15)</f>
         <v>28072.222222222223</v>
       </c>
-      <c r="E12" s="2">
-        <f>ROUNDUP(D12,0)</f>
-        <v>28073</v>
-      </c>
-      <c r="F12" s="2">
-        <f>D12/60</f>
-        <v>467.87037037037038</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <f>TRUNC(F12/60,1)</f>
+      <c r="E14" s="29">
+        <f>TRUNC(D14/3600,1)</f>
         <v>7.7</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="22">
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="20">
         <f>ValueProperties!C4/ValueProperties!C7</f>
         <v>66.666666666666671</v>
       </c>
-      <c r="E13">
-        <f>ROUNDUP(D13,0)</f>
-        <v>67</v>
-      </c>
-      <c r="F13">
-        <f>TRUNC(D13/60,1)</f>
+      <c r="E15" s="27">
+        <f>TRUNC(D15/60,1)</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="G13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="22">
-        <f>D6+D9+D13*2+D12</f>
+      <c r="F15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="19">
+        <f>D6+D9+D15*2+D14</f>
         <v>74838.888888888891</v>
       </c>
-      <c r="E14">
-        <f>ROUNDUP(D14,0)</f>
-        <v>74839</v>
-      </c>
-      <c r="F14">
-        <f>TRUNC(D14/60,1)</f>
-        <v>1247.3</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <f>TRUNC(F14/60,1)</f>
+      <c r="E16" s="1">
+        <f>TRUNC(D16/3600,1)</f>
         <v>20.7</v>
       </c>
-      <c r="I14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="22">
-        <f>D14/3600</f>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="26" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A17" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="25">
+        <f>D16/3600</f>
         <v>20.788580246913579</v>
       </c>
-      <c r="E15" s="19">
-        <f>ROUNDUP(D15,0)</f>
+      <c r="E17" s="23">
+        <f>ROUNDUP(D17,0)</f>
         <v>21</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/omf-example-plugin/src/main/java/com/samares_engineering/omf/omf_example_plugin/features/excel_to_parametric/UAV MOE Equation.xlsx
+++ b/omf-example-plugin/src/main/java/com/samares_engineering/omf/omf_example_plugin/features/excel_to_parametric/UAV MOE Equation.xlsx
@@ -5,13 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\java\mdplugins\OMF\OMF_Private\omf-example-plugin\src\main\java\com\samares_engineering\omf\omf_example_plugin\features\excel_to_parametric\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Plugins\OMF_Private\omf-example-plugin\src\main\java\com\samares_engineering\omf\omf_example_plugin\features\excel_to_parametric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2AE45D-B832-477E-BAAF-ABFB79919A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49536D0-5DE2-4B5D-A098-7DA6590E691B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14670" windowHeight="10545" xr2:uid="{A22A8A54-8611-4DA6-995F-F1DD76DD8434}"/>
-    <workbookView xWindow="-105" yWindow="10440" windowWidth="14670" windowHeight="10545" activeTab="1" xr2:uid="{ECDD6195-D704-4DB1-91AF-46E52C29149A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A22A8A54-8611-4DA6-995F-F1DD76DD8434}"/>
+    <workbookView xWindow="-22308" yWindow="9144" windowWidth="17280" windowHeight="3240" xr2:uid="{ECDD6195-D704-4DB1-91AF-46E52C29149A}"/>
+    <workbookView xWindow="-11616" yWindow="8412" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{798562BD-691F-4049-8B94-C5F37D32337C}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{5DB4170F-FB00-4D33-A0EA-EE7DB350FAE6}"/>
   </bookViews>
   <sheets>
     <sheet name="ValueProperties" sheetId="1" r:id="rId1"/>
@@ -787,17 +789,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F39931-1C93-41B6-BB89-874B75E18699}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="88.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="88.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -808,7 +810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>20</v>
       </c>
@@ -822,7 +824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -836,7 +838,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>22</v>
       </c>
@@ -850,7 +852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>23</v>
       </c>
@@ -864,7 +866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>24</v>
       </c>
@@ -878,7 +880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
@@ -892,7 +894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
@@ -906,7 +908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -920,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>26</v>
       </c>
@@ -934,7 +936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>27</v>
       </c>
@@ -948,7 +950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>28</v>
       </c>
@@ -962,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>29</v>
       </c>
@@ -976,7 +978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>30</v>
       </c>
@@ -987,10 +989,10 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>31</v>
       </c>
@@ -1004,7 +1006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1026,15 +1028,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA56FD2-2E8C-4F98-9B5F-251C6FDF40B3}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -1051,7 +1053,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>33</v>
       </c>
@@ -1073,7 +1075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>35</v>
       </c>
@@ -1091,7 +1093,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
@@ -1110,7 +1112,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>58</v>
       </c>
@@ -1129,7 +1131,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>59</v>
       </c>
@@ -1151,7 +1153,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>36</v>
       </c>
@@ -1169,7 +1171,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>37</v>
       </c>
@@ -1191,7 +1193,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
@@ -1213,7 +1215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>65</v>
       </c>
@@ -1228,7 +1230,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>63</v>
       </c>
@@ -1247,7 +1249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>39</v>
       </c>
@@ -1269,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>40</v>
       </c>
@@ -1286,7 +1288,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>41</v>
       </c>
@@ -1308,7 +1310,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>42</v>
       </c>
@@ -1330,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>43</v>
       </c>
@@ -1352,7 +1354,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="26" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" s="26" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="23" t="s">
         <v>43</v>
       </c>
